--- a/product_selector_out/STM32H543-H553.xlsx
+++ b/product_selector_out/STM32H543-H553.xlsx
@@ -6576,9 +6576,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -6913,9 +6913,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -7250,9 +7250,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -7587,9 +7587,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY15" s="6" t="inlineStr">
@@ -7924,9 +7924,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -8261,9 +8261,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY17" s="6" t="inlineStr">
@@ -8598,9 +8598,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY18" s="6" t="inlineStr">
@@ -8935,9 +8935,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -9272,9 +9272,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY20" s="6" t="inlineStr">
@@ -9609,9 +9609,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY21" s="6" t="inlineStr">
@@ -9946,9 +9946,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY22" s="6" t="inlineStr">
@@ -10283,9 +10283,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -10620,9 +10620,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY24" s="6" t="inlineStr">
@@ -10957,9 +10957,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY25" s="6" t="inlineStr">
@@ -11063,7 +11063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11112,19 +11112,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32H543CE</t>
+          <t>STM32H553UG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -11134,14 +11134,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32H543RG</t>
+          <t>STM32H543CE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -11156,19 +11156,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32H553CG</t>
+          <t>STM32H543CE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -11178,14 +11178,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32H543CG</t>
+          <t>STM32H543RG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -11200,19 +11200,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32H543VG</t>
+          <t>STM32H543RG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -11222,14 +11222,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32H553ZG</t>
+          <t>STM32H553CG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -11244,19 +11244,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32H543VE</t>
+          <t>STM32H553CG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -11266,14 +11266,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32H543UG</t>
+          <t>STM32H543CG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -11288,19 +11288,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32H543RE</t>
+          <t>STM32H543CG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -11310,14 +11310,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32H553RG</t>
+          <t>STM32H543VG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -11332,19 +11332,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32H553VG</t>
+          <t>STM32H543VG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -11354,14 +11354,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32H543ZG</t>
+          <t>STM32H553ZG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -11376,29 +11376,337 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>STM32H553ZG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32H543VE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32H543VE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32H543UG</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32H543UG</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32H543RE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32H543RE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32H553RG</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32H553RG</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32H553VG</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32H553VG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32H543ZG</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32H543ZG</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>STM32H543ZE</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STM32H543ZE</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32H543-H553.xlsx
+++ b/product_selector_out/STM32H543-H553.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO25"/>
+  <dimension ref="A1:BP25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.86328125" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -907,6 +908,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1004,6 +1010,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1338,6 +1345,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h553cg.pdf</t>
         </is>
       </c>
@@ -1675,6 +1687,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -2012,6 +2029,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -2349,6 +2371,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h553cg.pdf</t>
         </is>
       </c>
@@ -2686,6 +2713,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -3023,6 +3055,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -3360,6 +3397,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h553cg.pdf</t>
         </is>
       </c>
@@ -3697,6 +3739,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -4034,6 +4081,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -4371,6 +4423,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -4708,6 +4765,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h553cg.pdf</t>
         </is>
       </c>
@@ -5045,6 +5107,11 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h553cg.pdf</t>
         </is>
       </c>
@@ -5382,6 +5449,11 @@
       </c>
       <c r="BO24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
@@ -5719,12 +5791,17 @@
       </c>
       <c r="BO25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h543ce.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -5747,12 +5824,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -5767,9 +5846,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -5819,7 +5897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO25"/>
+  <dimension ref="A1:BP25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5889,6 +5967,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6232,6 +6311,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -6329,6 +6413,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -6661,7 +6746,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6998,7 +7088,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7335,7 +7430,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7672,7 +7772,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8009,7 +8114,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8346,7 +8456,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8683,7 +8798,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9020,7 +9140,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9357,7 +9482,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9694,7 +9824,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10031,7 +10166,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10368,7 +10508,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10705,7 +10850,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO24" s="6" t="inlineStr">
+      <c r="BO24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11042,7 +11192,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="BO25" s="6" t="inlineStr">
+      <c r="BO25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11050,8 +11205,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
